--- a/data/trans_bre/IP16B10-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16B10-Clase-trans_bre.xlsx
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,19</t>
+          <t>0,0; 61,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 285,65</t>
+          <t>0,0; 161,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
